--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/67.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/67.xlsx
@@ -426,13 +426,13 @@
         <v>-15.20640659478292</v>
       </c>
       <c r="E2">
-        <v>-18.01050851731991</v>
+        <v>-22.57865195729746</v>
       </c>
       <c r="F2">
-        <v>2.463252214167367</v>
+        <v>2.269947710519685</v>
       </c>
       <c r="G2">
-        <v>-13.20925846237534</v>
+        <v>-14.69472816493481</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.13868341247856</v>
       </c>
       <c r="E3">
-        <v>-18.55014865091795</v>
+        <v>-21.8357920241312</v>
       </c>
       <c r="F3">
-        <v>3.02818718573299</v>
+        <v>2.879563163057508</v>
       </c>
       <c r="G3">
-        <v>-13.00706302743924</v>
+        <v>-14.06450722123382</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.05526833789339</v>
       </c>
       <c r="E4">
-        <v>-18.76573118452711</v>
+        <v>-21.83739963240392</v>
       </c>
       <c r="F4">
-        <v>3.122655861083051</v>
+        <v>2.497516803416765</v>
       </c>
       <c r="G4">
-        <v>-12.93135212117661</v>
+        <v>-14.7389130944543</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.06947101858449</v>
       </c>
       <c r="E5">
-        <v>-19.19982164595438</v>
+        <v>-23.68580951048477</v>
       </c>
       <c r="F5">
-        <v>2.788180984650278</v>
+        <v>2.328256492002742</v>
       </c>
       <c r="G5">
-        <v>-12.10293883284204</v>
+        <v>-13.52058732637857</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.17595038505905</v>
       </c>
       <c r="E6">
-        <v>-20.01177703552967</v>
+        <v>-23.91268605826906</v>
       </c>
       <c r="F6">
-        <v>3.00039048916465</v>
+        <v>2.537984207778327</v>
       </c>
       <c r="G6">
-        <v>-12.46761707818029</v>
+        <v>-14.74173822621698</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.39630539835471</v>
       </c>
       <c r="E7">
-        <v>-20.14341977493265</v>
+        <v>-23.59765823545146</v>
       </c>
       <c r="F7">
-        <v>2.783593485973574</v>
+        <v>2.748343139514844</v>
       </c>
       <c r="G7">
-        <v>-11.92323289047438</v>
+        <v>-12.46561553302903</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.730365287998081</v>
       </c>
       <c r="E8">
-        <v>-20.49064051947077</v>
+        <v>-24.54265113442409</v>
       </c>
       <c r="F8">
-        <v>3.137753685366475</v>
+        <v>2.637363445092183</v>
       </c>
       <c r="G8">
-        <v>-12.02627309110562</v>
+        <v>-13.70766617359032</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.192834114251756</v>
       </c>
       <c r="E9">
-        <v>-21.67436098270577</v>
+        <v>-25.47354236533684</v>
       </c>
       <c r="F9">
-        <v>2.531542822854158</v>
+        <v>3.088966158811195</v>
       </c>
       <c r="G9">
-        <v>-10.72828746662048</v>
+        <v>-12.81136441119084</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.785314365698623</v>
       </c>
       <c r="E10">
-        <v>-21.53827581030126</v>
+        <v>-25.55287217300321</v>
       </c>
       <c r="F10">
-        <v>2.632853812951343</v>
+        <v>3.362643838082902</v>
       </c>
       <c r="G10">
-        <v>-10.45883027093732</v>
+        <v>-12.88603845144068</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.503679438329423</v>
       </c>
       <c r="E11">
-        <v>-22.18788087822757</v>
+        <v>-26.15965599071299</v>
       </c>
       <c r="F11">
-        <v>2.713185570205228</v>
+        <v>3.223042393158712</v>
       </c>
       <c r="G11">
-        <v>-9.979725986156557</v>
+        <v>-13.74541826824251</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.342982434250478</v>
       </c>
       <c r="E12">
-        <v>-23.33208134879762</v>
+        <v>-27.10386546368229</v>
       </c>
       <c r="F12">
-        <v>2.63265169130506</v>
+        <v>2.847154116790381</v>
       </c>
       <c r="G12">
-        <v>-9.446327328231664</v>
+        <v>-11.05850960436299</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.298834268187143</v>
       </c>
       <c r="E13">
-        <v>-24.33294656007689</v>
+        <v>-27.50028354983975</v>
       </c>
       <c r="F13">
-        <v>3.571700576262219</v>
+        <v>2.336432478268374</v>
       </c>
       <c r="G13">
-        <v>-9.647659801897634</v>
+        <v>-10.85165155359092</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.379544150303994</v>
       </c>
       <c r="E14">
-        <v>-25.4248069280663</v>
+        <v>-28.44478284514555</v>
       </c>
       <c r="F14">
-        <v>3.56859419850172</v>
+        <v>3.477248468260213</v>
       </c>
       <c r="G14">
-        <v>-8.943312781947231</v>
+        <v>-10.29218030915468</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.57958349290509</v>
       </c>
       <c r="E15">
-        <v>-24.90831635359546</v>
+        <v>-30.45298445706105</v>
       </c>
       <c r="F15">
-        <v>3.804286262150653</v>
+        <v>4.184369391046761</v>
       </c>
       <c r="G15">
-        <v>-8.536257560168757</v>
+        <v>-9.771506228437314</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.880364322077574</v>
       </c>
       <c r="E16">
-        <v>-26.25090021349354</v>
+        <v>-28.75566258577212</v>
       </c>
       <c r="F16">
-        <v>4.151721774967627</v>
+        <v>3.495007008641429</v>
       </c>
       <c r="G16">
-        <v>-7.715932482978221</v>
+        <v>-9.746565663363976</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.2724041012359</v>
       </c>
       <c r="E17">
-        <v>-26.89700024253791</v>
+        <v>-30.72301509790143</v>
       </c>
       <c r="F17">
-        <v>4.043772248504406</v>
+        <v>3.780719209541007</v>
       </c>
       <c r="G17">
-        <v>-7.786842962099381</v>
+        <v>-10.20264889768367</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.741775244291087</v>
       </c>
       <c r="E18">
-        <v>-28.22880633429773</v>
+        <v>-33.0964698378536</v>
       </c>
       <c r="F18">
-        <v>4.384559284546512</v>
+        <v>4.637037385245773</v>
       </c>
       <c r="G18">
-        <v>-8.457839646119588</v>
+        <v>-10.70264143891186</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.27350524268285</v>
       </c>
       <c r="E19">
-        <v>-28.1992716268197</v>
+        <v>-31.76336407405358</v>
       </c>
       <c r="F19">
-        <v>4.296185736546249</v>
+        <v>3.627814184127857</v>
       </c>
       <c r="G19">
-        <v>-7.668453207013056</v>
+        <v>-10.14960795117525</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.84076358142105</v>
       </c>
       <c r="E20">
-        <v>-29.18191425869211</v>
+        <v>-31.00605604456585</v>
       </c>
       <c r="F20">
-        <v>4.859642900665278</v>
+        <v>4.552101561967128</v>
       </c>
       <c r="G20">
-        <v>-6.85061201454302</v>
+        <v>-9.76059616675216</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.4156298470248</v>
       </c>
       <c r="E21">
-        <v>-29.81065891110208</v>
+        <v>-32.3833370723107</v>
       </c>
       <c r="F21">
-        <v>5.267179782024968</v>
+        <v>5.276826948797972</v>
       </c>
       <c r="G21">
-        <v>-7.934182935004687</v>
+        <v>-8.792327371889382</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.97611814420045</v>
       </c>
       <c r="E22">
-        <v>-30.72752092953906</v>
+        <v>-33.89547605600396</v>
       </c>
       <c r="F22">
-        <v>5.174593157414067</v>
+        <v>4.709976791797075</v>
       </c>
       <c r="G22">
-        <v>-5.918023222917643</v>
+        <v>-8.309551400183603</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.50667762960117</v>
       </c>
       <c r="E23">
-        <v>-30.7823267862169</v>
+        <v>-34.28351193677322</v>
       </c>
       <c r="F23">
-        <v>4.820474376391306</v>
+        <v>5.026085106174977</v>
       </c>
       <c r="G23">
-        <v>-6.657289002703656</v>
+        <v>-10.21450723239951</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.9906709104199</v>
       </c>
       <c r="E24">
-        <v>-31.57250927276331</v>
+        <v>-34.75892925199449</v>
       </c>
       <c r="F24">
-        <v>5.373065016920412</v>
+        <v>5.234224013271993</v>
       </c>
       <c r="G24">
-        <v>-6.602837130924671</v>
+        <v>-9.253299626332652</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.4055008345654</v>
       </c>
       <c r="E25">
-        <v>-30.89591676398829</v>
+        <v>-33.88769160918478</v>
       </c>
       <c r="F25">
-        <v>5.486022852700959</v>
+        <v>5.131804667589862</v>
       </c>
       <c r="G25">
-        <v>-6.006527612040546</v>
+        <v>-9.843909663368022</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.74228212380964</v>
       </c>
       <c r="E26">
-        <v>-31.86185611948341</v>
+        <v>-35.47040233181359</v>
       </c>
       <c r="F26">
-        <v>5.146562861238138</v>
+        <v>5.289565582718222</v>
       </c>
       <c r="G26">
-        <v>-5.458265020451369</v>
+        <v>-9.521290115978738</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.99366584864968</v>
       </c>
       <c r="E27">
-        <v>-31.32496250537102</v>
+        <v>-34.50379049792834</v>
       </c>
       <c r="F27">
-        <v>5.236116004419987</v>
+        <v>5.3590357865866</v>
       </c>
       <c r="G27">
-        <v>-6.308206403437452</v>
+        <v>-8.40245262619616</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-14.15959751808908</v>
       </c>
       <c r="E28">
-        <v>-31.52890459654345</v>
+        <v>-35.61854683050051</v>
       </c>
       <c r="F28">
-        <v>5.63554648237588</v>
+        <v>5.355223639798917</v>
       </c>
       <c r="G28">
-        <v>-5.664063236659741</v>
+        <v>-8.071393776955986</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.23495532165745</v>
       </c>
       <c r="E29">
-        <v>-32.15978216021104</v>
+        <v>-35.63619655794541</v>
       </c>
       <c r="F29">
-        <v>5.55026274478806</v>
+        <v>5.399652297080666</v>
       </c>
       <c r="G29">
-        <v>-5.115406898483431</v>
+        <v>-8.748923373101047</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.21330317141278</v>
       </c>
       <c r="E30">
-        <v>-30.37589397979148</v>
+        <v>-36.81467531251653</v>
       </c>
       <c r="F30">
-        <v>5.290766715452281</v>
+        <v>5.391688372870151</v>
       </c>
       <c r="G30">
-        <v>-6.227393197649888</v>
+        <v>-8.537090990444856</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.09659352634107</v>
       </c>
       <c r="E31">
-        <v>-31.50357910565556</v>
+        <v>-36.47473182570872</v>
       </c>
       <c r="F31">
-        <v>5.486837966225314</v>
+        <v>4.525916868364637</v>
       </c>
       <c r="G31">
-        <v>-5.37393434515208</v>
+        <v>-9.057112108071893</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-13.89340528699482</v>
       </c>
       <c r="E32">
-        <v>-31.51639921557127</v>
+        <v>-36.98570898307522</v>
       </c>
       <c r="F32">
-        <v>5.002640651940946</v>
+        <v>4.382388961951177</v>
       </c>
       <c r="G32">
-        <v>-5.876482957975073</v>
+        <v>-7.766686418059712</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.6133196142703</v>
       </c>
       <c r="E33">
-        <v>-31.7651437643386</v>
+        <v>-35.28127514335724</v>
       </c>
       <c r="F33">
-        <v>4.875337149478718</v>
+        <v>4.993215487631893</v>
       </c>
       <c r="G33">
-        <v>-5.457812211876165</v>
+        <v>-8.727766056485748</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.2612759808195</v>
       </c>
       <c r="E34">
-        <v>-31.14153440145332</v>
+        <v>-33.55646769907875</v>
       </c>
       <c r="F34">
-        <v>4.660682304391282</v>
+        <v>4.705225276374617</v>
       </c>
       <c r="G34">
-        <v>-5.62495435689272</v>
+        <v>-8.496456342652692</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.8486994198776</v>
       </c>
       <c r="E35">
-        <v>-30.68397738771831</v>
+        <v>-33.79576811530308</v>
       </c>
       <c r="F35">
-        <v>5.11463592479944</v>
+        <v>5.079195053838065</v>
       </c>
       <c r="G35">
-        <v>-5.760885522435836</v>
+        <v>-8.828155030096958</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.38641400121721</v>
       </c>
       <c r="E36">
-        <v>-29.68905579857411</v>
+        <v>-32.07023837942037</v>
       </c>
       <c r="F36">
-        <v>4.644202763279988</v>
+        <v>4.191909191147042</v>
       </c>
       <c r="G36">
-        <v>-5.589769818110794</v>
+        <v>-8.835117782246101</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.89896463169361</v>
       </c>
       <c r="E37">
-        <v>-29.70698629140748</v>
+        <v>-33.8992120470603</v>
       </c>
       <c r="F37">
-        <v>5.108568961941335</v>
+        <v>4.312413453967092</v>
       </c>
       <c r="G37">
-        <v>-5.275005515134821</v>
+        <v>-9.873847528876395</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.40122658321674</v>
       </c>
       <c r="E38">
-        <v>-29.09261275126085</v>
+        <v>-33.34123838644219</v>
       </c>
       <c r="F38">
-        <v>4.938773525185105</v>
+        <v>4.708144443102083</v>
       </c>
       <c r="G38">
-        <v>-5.911149063750607</v>
+        <v>-8.552614449642588</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.90229757767622</v>
       </c>
       <c r="E39">
-        <v>-30.02993441526449</v>
+        <v>-33.30062929577841</v>
       </c>
       <c r="F39">
-        <v>5.167134537319261</v>
+        <v>5.018778905682286</v>
       </c>
       <c r="G39">
-        <v>-5.864719778684464</v>
+        <v>-9.786478442413062</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.41580515245523</v>
       </c>
       <c r="E40">
-        <v>-27.78019305672786</v>
+        <v>-33.26952773629373</v>
       </c>
       <c r="F40">
-        <v>4.817858392133266</v>
+        <v>5.08767090910351</v>
       </c>
       <c r="G40">
-        <v>-6.230365984382745</v>
+        <v>-9.163866651508426</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.957359962977964</v>
       </c>
       <c r="E41">
-        <v>-29.56221777009327</v>
+        <v>-31.9505870391897</v>
       </c>
       <c r="F41">
-        <v>5.442601490181014</v>
+        <v>5.281575150750818</v>
       </c>
       <c r="G41">
-        <v>-5.91951945994875</v>
+        <v>-9.346387881974097</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.543136110511771</v>
       </c>
       <c r="E42">
-        <v>-27.88630425967559</v>
+        <v>-30.50422187622084</v>
       </c>
       <c r="F42">
-        <v>5.1595417217052</v>
+        <v>4.870410020166867</v>
       </c>
       <c r="G42">
-        <v>-6.32180706680135</v>
+        <v>-8.986477251561725</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.178403498937437</v>
       </c>
       <c r="E43">
-        <v>-26.71919876757474</v>
+        <v>-31.36060838852239</v>
       </c>
       <c r="F43">
-        <v>5.303034836687742</v>
+        <v>4.933586288508774</v>
       </c>
       <c r="G43">
-        <v>-6.269481426592885</v>
+        <v>-10.00931604217963</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.866050798513404</v>
       </c>
       <c r="E44">
-        <v>-26.99538586882855</v>
+        <v>-31.52642072855025</v>
       </c>
       <c r="F44">
-        <v>5.28702912173085</v>
+        <v>4.467772103627333</v>
       </c>
       <c r="G44">
-        <v>-6.003761542265933</v>
+        <v>-9.52358368984879</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.605749003531342</v>
       </c>
       <c r="E45">
-        <v>-27.51121075762026</v>
+        <v>-29.66798707325342</v>
       </c>
       <c r="F45">
-        <v>5.232476158052086</v>
+        <v>4.357786450088032</v>
       </c>
       <c r="G45">
-        <v>-6.804310697117696</v>
+        <v>-9.898374660033245</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.405318479316172</v>
       </c>
       <c r="E46">
-        <v>-25.67593798263566</v>
+        <v>-25.58752405610991</v>
       </c>
       <c r="F46">
-        <v>5.626919864243126</v>
+        <v>5.205922012587945</v>
       </c>
       <c r="G46">
-        <v>-6.816756370492669</v>
+        <v>-10.28633973477887</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.262425748285262</v>
       </c>
       <c r="E47">
-        <v>-25.63154988041248</v>
+        <v>-29.2825731789346</v>
       </c>
       <c r="F47">
-        <v>5.197008779333822</v>
+        <v>4.821640717694448</v>
       </c>
       <c r="G47">
-        <v>-5.837846574112612</v>
+        <v>-10.15088434636187</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.165589651738538</v>
       </c>
       <c r="E48">
-        <v>-24.24090079739699</v>
+        <v>-29.81892111192907</v>
       </c>
       <c r="F48">
-        <v>5.394647301232951</v>
+        <v>5.099725311549048</v>
       </c>
       <c r="G48">
-        <v>-7.150804412573498</v>
+        <v>-7.579167887159006</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.10797276886281</v>
       </c>
       <c r="E49">
-        <v>-24.93099042295187</v>
+        <v>-27.97832285151146</v>
       </c>
       <c r="F49">
-        <v>5.195154893086356</v>
+        <v>4.542376528658263</v>
       </c>
       <c r="G49">
-        <v>-6.173348197344274</v>
+        <v>-9.384066149141201</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.081747829598763</v>
       </c>
       <c r="E50">
-        <v>-23.95953765035241</v>
+        <v>-26.44951908346996</v>
       </c>
       <c r="F50">
-        <v>5.565943739723055</v>
+        <v>5.425603391075568</v>
       </c>
       <c r="G50">
-        <v>-6.711507907751921</v>
+        <v>-10.36818980657922</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.083946970343197</v>
       </c>
       <c r="E51">
-        <v>-22.77972526018604</v>
+        <v>-25.3912781065135</v>
       </c>
       <c r="F51">
-        <v>5.287488037272001</v>
+        <v>4.710879712266126</v>
       </c>
       <c r="G51">
-        <v>-7.112971927993101</v>
+        <v>-9.329273030320033</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.104360866915338</v>
       </c>
       <c r="E52">
-        <v>-21.71149446956866</v>
+        <v>-25.21264792080694</v>
       </c>
       <c r="F52">
-        <v>6.013041791505644</v>
+        <v>5.198034298178488</v>
       </c>
       <c r="G52">
-        <v>-7.004566930112166</v>
+        <v>-10.28933220884108</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.131638033852534</v>
       </c>
       <c r="E53">
-        <v>-21.98399539298023</v>
+        <v>-25.40526203424919</v>
       </c>
       <c r="F53">
-        <v>5.483946963989543</v>
+        <v>4.813625434704961</v>
       </c>
       <c r="G53">
-        <v>-7.067231699454442</v>
+        <v>-10.72618420360087</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.159643861229423</v>
       </c>
       <c r="E54">
-        <v>-20.97584839549662</v>
+        <v>-24.12410239579115</v>
       </c>
       <c r="F54">
-        <v>5.319960039461741</v>
+        <v>5.195431567798892</v>
       </c>
       <c r="G54">
-        <v>-7.28593824127767</v>
+        <v>-10.35097651827837</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.188129886871367</v>
       </c>
       <c r="E55">
-        <v>-21.05904551996554</v>
+        <v>-24.84840011399997</v>
       </c>
       <c r="F55">
-        <v>5.10057190303471</v>
+        <v>4.739735062375245</v>
       </c>
       <c r="G55">
-        <v>-6.860921612682795</v>
+        <v>-9.896113898378786</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.215954925938506</v>
       </c>
       <c r="E56">
-        <v>-21.16590844959855</v>
+        <v>-23.27089713647999</v>
       </c>
       <c r="F56">
-        <v>5.152421075510736</v>
+        <v>4.174733821417397</v>
       </c>
       <c r="G56">
-        <v>-7.306422907473283</v>
+        <v>-9.715462964201999</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.236912094382941</v>
       </c>
       <c r="E57">
-        <v>-20.45398705085269</v>
+        <v>-24.74153265589296</v>
       </c>
       <c r="F57">
-        <v>4.91308253855468</v>
+        <v>4.119975422622739</v>
       </c>
       <c r="G57">
-        <v>-7.81320429610796</v>
+        <v>-10.73028901177174</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.250220096813544</v>
       </c>
       <c r="E58">
-        <v>-19.51270297209233</v>
+        <v>-22.17543663165449</v>
       </c>
       <c r="F58">
-        <v>4.932627039056332</v>
+        <v>4.609098209484151</v>
       </c>
       <c r="G58">
-        <v>-7.165989905950608</v>
+        <v>-10.86376910480995</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.255390324821823</v>
       </c>
       <c r="E59">
-        <v>-19.58814734906013</v>
+        <v>-22.30572082885517</v>
       </c>
       <c r="F59">
-        <v>4.912247544212659</v>
+        <v>4.46606069657315</v>
       </c>
       <c r="G59">
-        <v>-8.022497013277141</v>
+        <v>-9.288674475965024</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.258413111626298</v>
       </c>
       <c r="E60">
-        <v>-19.13926689152381</v>
+        <v>-22.80730366689275</v>
       </c>
       <c r="F60">
-        <v>4.486473326112935</v>
+        <v>4.743232429549864</v>
       </c>
       <c r="G60">
-        <v>-8.318561634585837</v>
+        <v>-10.49221341908311</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.258854423118631</v>
       </c>
       <c r="E61">
-        <v>-18.40868365139234</v>
+        <v>-22.16444602523788</v>
       </c>
       <c r="F61">
-        <v>4.954273936026289</v>
+        <v>4.459483459394922</v>
       </c>
       <c r="G61">
-        <v>-7.960688642761881</v>
+        <v>-10.55602005352807</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.251715255679892</v>
       </c>
       <c r="E62">
-        <v>-17.94956884259869</v>
+        <v>-22.56492615258021</v>
       </c>
       <c r="F62">
-        <v>4.833946943830438</v>
+        <v>3.701775796054214</v>
       </c>
       <c r="G62">
-        <v>-7.990262292677156</v>
+        <v>-9.541896187372052</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.237741161253139</v>
       </c>
       <c r="E63">
-        <v>-17.38176612914694</v>
+        <v>-20.07527982653923</v>
       </c>
       <c r="F63">
-        <v>4.81009824630384</v>
+        <v>3.618382392879582</v>
       </c>
       <c r="G63">
-        <v>-7.176758875108706</v>
+        <v>-10.24323432715244</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.218687206222953</v>
       </c>
       <c r="E64">
-        <v>-16.42395312025859</v>
+        <v>-20.05320804422585</v>
       </c>
       <c r="F64">
-        <v>4.533801269304482</v>
+        <v>4.506271307039843</v>
       </c>
       <c r="G64">
-        <v>-8.065592577238888</v>
+        <v>-10.82786597850651</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.197059413127853</v>
       </c>
       <c r="E65">
-        <v>-16.89841945593825</v>
+        <v>-20.17151442767624</v>
       </c>
       <c r="F65">
-        <v>4.629885261090002</v>
+        <v>3.814606063254729</v>
       </c>
       <c r="G65">
-        <v>-8.432049244662352</v>
+        <v>-10.28044666085811</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.169449979814075</v>
       </c>
       <c r="E66">
-        <v>-16.31483048209576</v>
+        <v>-19.79903838359733</v>
       </c>
       <c r="F66">
-        <v>4.094276152318287</v>
+        <v>4.180020462182063</v>
       </c>
       <c r="G66">
-        <v>-7.616623031260067</v>
+        <v>-9.736101847810906</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.134536964461162</v>
       </c>
       <c r="E67">
-        <v>-16.81725108782476</v>
+        <v>-19.67488121172903</v>
       </c>
       <c r="F67">
-        <v>4.344390092449959</v>
+        <v>3.66687336390466</v>
       </c>
       <c r="G67">
-        <v>-8.310716233837205</v>
+        <v>-10.16573515513992</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.091960664249092</v>
       </c>
       <c r="E68">
-        <v>-17.33668064192658</v>
+        <v>-19.3974351947011</v>
       </c>
       <c r="F68">
-        <v>4.362095617317395</v>
+        <v>3.479223296148487</v>
       </c>
       <c r="G68">
-        <v>-7.44128111356646</v>
+        <v>-9.546371773579134</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.04900715467382</v>
       </c>
       <c r="E69">
-        <v>-15.58497179780552</v>
+        <v>-18.6258058661641</v>
       </c>
       <c r="F69">
-        <v>3.848151629598497</v>
+        <v>3.486193179475642</v>
       </c>
       <c r="G69">
-        <v>-8.058190141400781</v>
+        <v>-10.55064213139214</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.008295989491776</v>
       </c>
       <c r="E70">
-        <v>-17.05969200077341</v>
+        <v>-20.85554042653484</v>
       </c>
       <c r="F70">
-        <v>3.644305322382789</v>
+        <v>3.596480358749563</v>
       </c>
       <c r="G70">
-        <v>-6.932065058534675</v>
+        <v>-9.197000426815698</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.966320514633122</v>
       </c>
       <c r="E71">
-        <v>-16.45583357727259</v>
+        <v>-18.82987701884576</v>
       </c>
       <c r="F71">
-        <v>3.30657661879182</v>
+        <v>3.780929614861318</v>
       </c>
       <c r="G71">
-        <v>-6.252688134651647</v>
+        <v>-8.948483987124915</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.92657010998601</v>
       </c>
       <c r="E72">
-        <v>-16.14431532181094</v>
+        <v>-19.46036286951168</v>
       </c>
       <c r="F72">
-        <v>3.490566959362424</v>
+        <v>3.297002348350263</v>
       </c>
       <c r="G72">
-        <v>-7.016536826361021</v>
+        <v>-10.23508049157722</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.891936274237006</v>
       </c>
       <c r="E73">
-        <v>-16.04054986839918</v>
+        <v>-18.59259403779185</v>
       </c>
       <c r="F73">
-        <v>3.163583837720569</v>
+        <v>3.410896239295973</v>
       </c>
       <c r="G73">
-        <v>-6.911606642111538</v>
+        <v>-9.202535847586482</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.868496417926874</v>
       </c>
       <c r="E74">
-        <v>-15.68703001651639</v>
+        <v>-18.75466359405236</v>
       </c>
       <c r="F74">
-        <v>3.743457587028279</v>
+        <v>2.749362031420288</v>
       </c>
       <c r="G74">
-        <v>-6.229447242346101</v>
+        <v>-9.985756871382817</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.855603547767911</v>
       </c>
       <c r="E75">
-        <v>-14.71424134408467</v>
+        <v>-18.11587252205637</v>
       </c>
       <c r="F75">
-        <v>3.130149272608776</v>
+        <v>2.69235213002482</v>
       </c>
       <c r="G75">
-        <v>-6.163993434678297</v>
+        <v>-10.25333392711241</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.850416446363072</v>
       </c>
       <c r="E76">
-        <v>-15.64455293032444</v>
+        <v>-18.27556010098886</v>
       </c>
       <c r="F76">
-        <v>2.798325171864961</v>
+        <v>2.829987030734764</v>
       </c>
       <c r="G76">
-        <v>-6.237883262975433</v>
+        <v>-10.1545232210713</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.852639301884678</v>
       </c>
       <c r="E77">
-        <v>-16.69034966070782</v>
+        <v>-19.23281610757426</v>
       </c>
       <c r="F77">
-        <v>2.805797045838212</v>
+        <v>2.619687741451247</v>
       </c>
       <c r="G77">
-        <v>-6.212939416680534</v>
+        <v>-9.472708349569601</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.865956513907238</v>
       </c>
       <c r="E78">
-        <v>-16.68061797006533</v>
+        <v>-20.26114651371006</v>
       </c>
       <c r="F78">
-        <v>3.054335431169759</v>
+        <v>2.770101037716776</v>
       </c>
       <c r="G78">
-        <v>-6.507740767688845</v>
+        <v>-9.436667411960659</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.890998454911867</v>
       </c>
       <c r="E79">
-        <v>-17.12304535214072</v>
+        <v>-20.90297166329118</v>
       </c>
       <c r="F79">
-        <v>3.192695981724555</v>
+        <v>2.961945958000725</v>
       </c>
       <c r="G79">
-        <v>-5.023890347968958</v>
+        <v>-9.863045747502703</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.922037890259141</v>
       </c>
       <c r="E80">
-        <v>-17.43843545287893</v>
+        <v>-20.98727373541797</v>
       </c>
       <c r="F80">
-        <v>3.121600521011885</v>
+        <v>2.767016197508751</v>
       </c>
       <c r="G80">
-        <v>-5.399941307232239</v>
+        <v>-8.957940467659235</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.958444174514518</v>
       </c>
       <c r="E81">
-        <v>-17.1169545546004</v>
+        <v>-20.45964311488827</v>
       </c>
       <c r="F81">
-        <v>2.957187815639045</v>
+        <v>2.463674681542794</v>
       </c>
       <c r="G81">
-        <v>-4.836640877236126</v>
+        <v>-8.506677347810363</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.000088353193576</v>
       </c>
       <c r="E82">
-        <v>-18.82273108686166</v>
+        <v>-22.57066372914793</v>
       </c>
       <c r="F82">
-        <v>2.71368921758613</v>
+        <v>2.179582767283093</v>
       </c>
       <c r="G82">
-        <v>-6.235960467141599</v>
+        <v>-8.493030747344632</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.053588032350552</v>
       </c>
       <c r="E83">
-        <v>-18.56725269724493</v>
+        <v>-22.93391980014722</v>
       </c>
       <c r="F83">
-        <v>2.515141148278727</v>
+        <v>2.41165155191218</v>
       </c>
       <c r="G83">
-        <v>-5.80648137722588</v>
+        <v>-8.698146469468639</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.120428418886638</v>
       </c>
       <c r="E84">
-        <v>-20.67050697858143</v>
+        <v>-23.98450765603071</v>
       </c>
       <c r="F84">
-        <v>2.707292564501712</v>
+        <v>2.182733876883342</v>
       </c>
       <c r="G84">
-        <v>-4.763768227622418</v>
+        <v>-8.945117453804926</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.198238631588902</v>
       </c>
       <c r="E85">
-        <v>-20.1180059788016</v>
+        <v>-24.59820645355019</v>
       </c>
       <c r="F85">
-        <v>2.244573160237131</v>
+        <v>2.55910923328452</v>
       </c>
       <c r="G85">
-        <v>-4.52774996085156</v>
+        <v>-7.072015720488112</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.292782989379308</v>
       </c>
       <c r="E86">
-        <v>-22.01803140362188</v>
+        <v>-25.11337018513678</v>
       </c>
       <c r="F86">
-        <v>2.496820974798414</v>
+        <v>2.047317344078095</v>
       </c>
       <c r="G86">
-        <v>-4.686134525525957</v>
+        <v>-7.833580681992111</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.411509292590107</v>
       </c>
       <c r="E87">
-        <v>-23.48559208918364</v>
+        <v>-25.86713468371351</v>
       </c>
       <c r="F87">
-        <v>2.555409744463617</v>
+        <v>1.862836610005034</v>
       </c>
       <c r="G87">
-        <v>-4.817134015065228</v>
+        <v>-8.081509783023755</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.56152016695788</v>
       </c>
       <c r="E88">
-        <v>-23.78626917787093</v>
+        <v>-27.48023599540779</v>
       </c>
       <c r="F88">
-        <v>2.295381903255241</v>
+        <v>2.093984250082209</v>
       </c>
       <c r="G88">
-        <v>-4.591625500949271</v>
+        <v>-7.962079880703086</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.741257407747218</v>
       </c>
       <c r="E89">
-        <v>-26.09518863473979</v>
+        <v>-28.79322174919174</v>
       </c>
       <c r="F89">
-        <v>1.944616353479013</v>
+        <v>1.467682164582392</v>
       </c>
       <c r="G89">
-        <v>-5.219073812432527</v>
+        <v>-7.422181122868933</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.951190616242631</v>
       </c>
       <c r="E90">
-        <v>-27.27269603163626</v>
+        <v>-30.92956785433929</v>
       </c>
       <c r="F90">
-        <v>1.736417803928996</v>
+        <v>1.994103022122255</v>
       </c>
       <c r="G90">
-        <v>-4.824753011526258</v>
+        <v>-6.813183120214434</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.192793290394489</v>
       </c>
       <c r="E91">
-        <v>-28.56535799407378</v>
+        <v>-33.02247683680528</v>
       </c>
       <c r="F91">
-        <v>1.719992935066288</v>
+        <v>1.970355385418799</v>
       </c>
       <c r="G91">
-        <v>-5.116745636879684</v>
+        <v>-7.322993076348479</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.472941307057757</v>
       </c>
       <c r="E92">
-        <v>-31.21883545276426</v>
+        <v>-33.03799138875555</v>
       </c>
       <c r="F92">
-        <v>1.800147421695973</v>
+        <v>0.975890377949159</v>
       </c>
       <c r="G92">
-        <v>-4.977073878758801</v>
+        <v>-7.687500698165633</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.792685974641824</v>
       </c>
       <c r="E93">
-        <v>-32.05449966800671</v>
+        <v>-34.42060243040743</v>
       </c>
       <c r="F93">
-        <v>2.171449856122407</v>
+        <v>1.101450995395897</v>
       </c>
       <c r="G93">
-        <v>-4.623118665476821</v>
+        <v>-8.468398617097881</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.14030291758433</v>
       </c>
       <c r="E94">
-        <v>-33.54751717020259</v>
+        <v>-35.35796711491415</v>
       </c>
       <c r="F94">
-        <v>1.455028024137227</v>
+        <v>0.453772889066839</v>
       </c>
       <c r="G94">
-        <v>-4.161864225979439</v>
+        <v>-7.643542172933752</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.51661413844891</v>
       </c>
       <c r="E95">
-        <v>-36.41385781386062</v>
+        <v>-38.89786845399905</v>
       </c>
       <c r="F95">
-        <v>1.354441027150088</v>
+        <v>0.8315291339284836</v>
       </c>
       <c r="G95">
-        <v>-5.035502591067833</v>
+        <v>-7.066263739094405</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.92317076260682</v>
       </c>
       <c r="E96">
-        <v>-38.17663198421941</v>
+        <v>-38.40577729748154</v>
       </c>
       <c r="F96">
-        <v>1.024068226095978</v>
+        <v>0.4670052299591583</v>
       </c>
       <c r="G96">
-        <v>-5.02517658682026</v>
+        <v>-8.480194608604084</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.35596052029088</v>
       </c>
       <c r="E97">
-        <v>-39.67667314960119</v>
+        <v>-42.73409728248688</v>
       </c>
       <c r="F97">
-        <v>1.146090057997957</v>
+        <v>0.4002040258626006</v>
       </c>
       <c r="G97">
-        <v>-4.841142713215684</v>
+        <v>-8.743069673838997</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.81577513213483</v>
       </c>
       <c r="E98">
-        <v>-42.96980435458612</v>
+        <v>-42.78067943036678</v>
       </c>
       <c r="F98">
-        <v>1.281095720571414</v>
+        <v>0.2852373991302656</v>
       </c>
       <c r="G98">
-        <v>-5.169793145831227</v>
+        <v>-9.635876935277667</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.27983189133528</v>
       </c>
       <c r="E99">
-        <v>-45.20679353031715</v>
+        <v>-45.77585289530602</v>
       </c>
       <c r="F99">
-        <v>0.9125799140879984</v>
+        <v>0.2164597104106283</v>
       </c>
       <c r="G99">
-        <v>-5.513773445572495</v>
+        <v>-9.190825167840824</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.76380644224323</v>
       </c>
       <c r="E100">
-        <v>-46.63391494299042</v>
+        <v>-48.5529010884808</v>
       </c>
       <c r="F100">
-        <v>0.7606175707792346</v>
+        <v>-0.1606868560425559</v>
       </c>
       <c r="G100">
-        <v>-6.414770636023538</v>
+        <v>-8.778562647447512</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.23369483728211</v>
       </c>
       <c r="E101">
-        <v>-48.26784497088298</v>
+        <v>-50.32512958044911</v>
       </c>
       <c r="F101">
-        <v>0.7286657833184522</v>
+        <v>0.1463649175205397</v>
       </c>
       <c r="G101">
-        <v>-5.52431929166455</v>
+        <v>-9.652486478811577</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.73854760623544</v>
       </c>
       <c r="E102">
-        <v>-49.6232104486677</v>
+        <v>-51.54819455798125</v>
       </c>
       <c r="F102">
-        <v>0.8012904102566905</v>
+        <v>0.06422814769595471</v>
       </c>
       <c r="G102">
-        <v>-7.067376073203057</v>
+        <v>-8.97197753349054</v>
       </c>
     </row>
   </sheetData>
